--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.13276227054996</v>
+        <v>8.63407386896437</v>
       </c>
       <c r="D2" t="n">
-        <v>29.90667360113605</v>
+        <v>4.859834460184608</v>
       </c>
       <c r="E2" t="n">
-        <v>12.80607629603882</v>
+        <v>2.080987398106308</v>
       </c>
       <c r="F2" t="n">
-        <v>8.253907422343245</v>
+        <v>1.341259956130778</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5509380388363</v>
+        <v>5.289527431310899</v>
       </c>
       <c r="D3" t="n">
-        <v>33.00156289744619</v>
+        <v>5.362753970835007</v>
       </c>
       <c r="E3" t="n">
-        <v>12.80607629603882</v>
+        <v>2.080987398106308</v>
       </c>
       <c r="F3" t="n">
-        <v>8.253907422343245</v>
+        <v>1.341259956130778</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.02745426523582</v>
+        <v>7.966961318100821</v>
       </c>
       <c r="D4" t="n">
-        <v>49.77099351967593</v>
+        <v>8.087786446947339</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80607629603882</v>
+        <v>2.080987398106308</v>
       </c>
       <c r="F4" t="n">
-        <v>8.253907422343245</v>
+        <v>1.341259956130778</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.27693064748244</v>
+        <v>3.457501230215897</v>
       </c>
       <c r="D5" t="n">
-        <v>29.89625113103109</v>
+        <v>4.858140808792553</v>
       </c>
       <c r="E5" t="n">
-        <v>12.80607629603882</v>
+        <v>2.080987398106308</v>
       </c>
       <c r="F5" t="n">
-        <v>8.253907422343245</v>
+        <v>1.341259956130778</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
